--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.59417419941056</v>
+        <v>2.696553307404216</v>
       </c>
       <c r="D2" t="n">
-        <v>15.83246122653123</v>
+        <v>2.572774949311325</v>
       </c>
       <c r="E2" t="n">
-        <v>2.384014073812377</v>
+        <v>0.3874022869945112</v>
       </c>
       <c r="F2" t="n">
-        <v>2.923078840397434</v>
+        <v>0.4750003115645831</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.71381036900083</v>
+        <v>3.690994184962635</v>
       </c>
       <c r="D3" t="n">
-        <v>9.7356789036258</v>
+        <v>1.582047821839192</v>
       </c>
       <c r="E3" t="n">
-        <v>2.384014073812377</v>
+        <v>0.3874022869945112</v>
       </c>
       <c r="F3" t="n">
-        <v>2.923078840397434</v>
+        <v>0.4750003115645831</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.23703230983842</v>
+        <v>2.963517750348744</v>
       </c>
       <c r="D4" t="n">
-        <v>13.5092560861063</v>
+        <v>2.195254113992273</v>
       </c>
       <c r="E4" t="n">
-        <v>2.384014073812377</v>
+        <v>0.3874022869945112</v>
       </c>
       <c r="F4" t="n">
-        <v>2.923078840397434</v>
+        <v>0.4750003115645831</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.29466339099012</v>
+        <v>2.810382801035895</v>
       </c>
       <c r="D5" t="n">
-        <v>17.53380432470307</v>
+        <v>2.849243202764249</v>
       </c>
       <c r="E5" t="n">
-        <v>2.384014073812377</v>
+        <v>0.3874022869945112</v>
       </c>
       <c r="F5" t="n">
-        <v>2.923078840397434</v>
+        <v>0.4750003115645831</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
